--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/86.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/86.xlsx
@@ -426,13 +426,13 @@
         <v>-6.61276141723632</v>
       </c>
       <c r="E2">
-        <v>-15.20654986735455</v>
+        <v>-11.35686694258993</v>
       </c>
       <c r="F2">
-        <v>-4.30485738101377</v>
+        <v>-3.976630879900314</v>
       </c>
       <c r="G2">
-        <v>-9.452125246727203</v>
+        <v>-8.445807406661103</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.460066501059012</v>
       </c>
       <c r="E3">
-        <v>-15.59059163404904</v>
+        <v>-12.56380489206225</v>
       </c>
       <c r="F3">
-        <v>-4.180698361212569</v>
+        <v>-3.520765387526495</v>
       </c>
       <c r="G3">
-        <v>-9.426039535329618</v>
+        <v>-8.780229507999708</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.421366256561975</v>
       </c>
       <c r="E4">
-        <v>-16.22306548480433</v>
+        <v>-13.43285528192625</v>
       </c>
       <c r="F4">
-        <v>-3.968029112789643</v>
+        <v>-3.481534735697314</v>
       </c>
       <c r="G4">
-        <v>-9.937601663776405</v>
+        <v>-8.268565661684578</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.488358026723033</v>
       </c>
       <c r="E5">
-        <v>-16.54231384539707</v>
+        <v>-13.30227673391508</v>
       </c>
       <c r="F5">
-        <v>-4.208454467778172</v>
+        <v>-3.154572323240529</v>
       </c>
       <c r="G5">
-        <v>-9.545479281314964</v>
+        <v>-8.151268553377548</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.612734780690267</v>
       </c>
       <c r="E6">
-        <v>-16.93854626412021</v>
+        <v>-14.44051773269104</v>
       </c>
       <c r="F6">
-        <v>-4.176045421511044</v>
+        <v>-3.406839190252076</v>
       </c>
       <c r="G6">
-        <v>-9.274939282517188</v>
+        <v>-8.418327176100755</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.748084909444863</v>
       </c>
       <c r="E7">
-        <v>-17.85240137581611</v>
+        <v>-15.41472381748715</v>
       </c>
       <c r="F7">
-        <v>-3.692061826016599</v>
+        <v>-2.822527048400167</v>
       </c>
       <c r="G7">
-        <v>-9.456676301030154</v>
+        <v>-7.558821032268889</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.840545183738183</v>
       </c>
       <c r="E8">
-        <v>-18.42322910990498</v>
+        <v>-15.43136143099133</v>
       </c>
       <c r="F8">
-        <v>-3.496412214251593</v>
+        <v>-2.758876953903858</v>
       </c>
       <c r="G8">
-        <v>-10.02207015038119</v>
+        <v>-8.87843318805233</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.840690456028816</v>
       </c>
       <c r="E9">
-        <v>-19.32250706377018</v>
+        <v>-16.19733922396675</v>
       </c>
       <c r="F9">
-        <v>-3.260194965669286</v>
+        <v>-2.777892127635121</v>
       </c>
       <c r="G9">
-        <v>-9.07372821404892</v>
+        <v>-8.404378703251554</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.706286504664094</v>
       </c>
       <c r="E10">
-        <v>-18.52747911003556</v>
+        <v>-16.85696127639802</v>
       </c>
       <c r="F10">
-        <v>-3.444216784201196</v>
+        <v>-2.227659849101786</v>
       </c>
       <c r="G10">
-        <v>-9.028965789534976</v>
+        <v>-8.829815328206038</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.402608719172631</v>
       </c>
       <c r="E11">
-        <v>-20.0187599424495</v>
+        <v>-18.16012024158532</v>
       </c>
       <c r="F11">
-        <v>-2.795905805176399</v>
+        <v>-2.203271884395966</v>
       </c>
       <c r="G11">
-        <v>-8.76149701411684</v>
+        <v>-7.312135514208276</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.917223892847181</v>
       </c>
       <c r="E12">
-        <v>-20.9208093224074</v>
+        <v>-17.58833699948083</v>
       </c>
       <c r="F12">
-        <v>-2.844437366204214</v>
+        <v>-1.992158309955498</v>
       </c>
       <c r="G12">
-        <v>-8.749399150227166</v>
+        <v>-7.528555044604571</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.249345473417885</v>
       </c>
       <c r="E13">
-        <v>-20.66862313339424</v>
+        <v>-18.31713602085328</v>
       </c>
       <c r="F13">
-        <v>-2.575584098686412</v>
+        <v>-1.65978582999103</v>
       </c>
       <c r="G13">
-        <v>-8.363511088728671</v>
+        <v>-6.421382297465819</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.430698740987727</v>
       </c>
       <c r="E14">
-        <v>-21.64472664879957</v>
+        <v>-19.57919455594696</v>
       </c>
       <c r="F14">
-        <v>-2.21315016567435</v>
+        <v>-1.336931291484728</v>
       </c>
       <c r="G14">
-        <v>-7.995666464585562</v>
+        <v>-6.74886133398464</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.506428576447255</v>
       </c>
       <c r="E15">
-        <v>-21.93204021069023</v>
+        <v>-19.9749560133733</v>
       </c>
       <c r="F15">
-        <v>-1.914046577341115</v>
+        <v>-1.033214525085303</v>
       </c>
       <c r="G15">
-        <v>-7.784375483486678</v>
+        <v>-7.222305511575358</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.539822221677706</v>
       </c>
       <c r="E16">
-        <v>-22.74210269813031</v>
+        <v>-19.37225687921845</v>
       </c>
       <c r="F16">
-        <v>-1.489291251146835</v>
+        <v>-1.009485940832111</v>
       </c>
       <c r="G16">
-        <v>-7.852592079707534</v>
+        <v>-6.956641408014916</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.599233386129475</v>
       </c>
       <c r="E17">
-        <v>-23.96825496281718</v>
+        <v>-20.70091568154294</v>
       </c>
       <c r="F17">
-        <v>-1.365297076458791</v>
+        <v>-0.286147241033555</v>
       </c>
       <c r="G17">
-        <v>-7.006456913730406</v>
+        <v>-5.466018546996336</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7437829214842636</v>
       </c>
       <c r="E18">
-        <v>-24.35099705747147</v>
+        <v>-22.78980564332711</v>
       </c>
       <c r="F18">
-        <v>-0.8730737104086999</v>
+        <v>-0.3060711338056887</v>
       </c>
       <c r="G18">
-        <v>-6.784268995832607</v>
+        <v>-5.962408306952252</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.02580009944059342</v>
       </c>
       <c r="E19">
-        <v>-25.19716959664872</v>
+        <v>-23.85812247495063</v>
       </c>
       <c r="F19">
-        <v>-0.4898386435449394</v>
+        <v>-0.08560114955060026</v>
       </c>
       <c r="G19">
-        <v>-6.288919383111036</v>
+        <v>-4.352493354918499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.5279598411359457</v>
       </c>
       <c r="E20">
-        <v>-26.08783892142534</v>
+        <v>-23.19496368431937</v>
       </c>
       <c r="F20">
-        <v>-0.331417519596548</v>
+        <v>0.5836965176241219</v>
       </c>
       <c r="G20">
-        <v>-5.54937141827091</v>
+        <v>-4.073307337311586</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.9003510087654255</v>
       </c>
       <c r="E21">
-        <v>-26.67239698870547</v>
+        <v>-24.79380935983751</v>
       </c>
       <c r="F21">
-        <v>0.1011658785541875</v>
+        <v>0.4657825596726263</v>
       </c>
       <c r="G21">
-        <v>-5.644841840764514</v>
+        <v>-3.75596399418989</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.094922249858158</v>
       </c>
       <c r="E22">
-        <v>-26.74129772073217</v>
+        <v>-23.81820850504703</v>
       </c>
       <c r="F22">
-        <v>0.2454335170583466</v>
+        <v>0.7721186237997031</v>
       </c>
       <c r="G22">
-        <v>-5.551674835805641</v>
+        <v>-3.245543730845789</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.127387457198126</v>
       </c>
       <c r="E23">
-        <v>-28.44046720941624</v>
+        <v>-24.53555048718007</v>
       </c>
       <c r="F23">
-        <v>-0.08214934258313472</v>
+        <v>1.171131604584586</v>
       </c>
       <c r="G23">
-        <v>-4.82822782515771</v>
+        <v>-2.8774628587504</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.021497898568937</v>
       </c>
       <c r="E24">
-        <v>-28.89428823209492</v>
+        <v>-25.93382552042447</v>
       </c>
       <c r="F24">
-        <v>0.6493976498097619</v>
+        <v>1.03668591837542</v>
       </c>
       <c r="G24">
-        <v>-4.550774292534184</v>
+        <v>-3.470786466015432</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.811317407735769</v>
       </c>
       <c r="E25">
-        <v>-29.00293538048695</v>
+        <v>-25.13383435917744</v>
       </c>
       <c r="F25">
-        <v>0.1746544926935456</v>
+        <v>0.6986681145608736</v>
       </c>
       <c r="G25">
-        <v>-5.066506853583026</v>
+        <v>-3.711752814897932</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.5308573300517634</v>
       </c>
       <c r="E26">
-        <v>-28.96230138321613</v>
+        <v>-25.5110064308023</v>
       </c>
       <c r="F26">
-        <v>0.4056861613343277</v>
+        <v>1.480185542160248</v>
       </c>
       <c r="G26">
-        <v>-4.748031489023322</v>
+        <v>-3.695244989232366</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.2177863345958554</v>
       </c>
       <c r="E27">
-        <v>-29.94416964603322</v>
+        <v>-26.92503149664538</v>
       </c>
       <c r="F27">
-        <v>-0.065592763303381</v>
+        <v>0.4897637959836719</v>
       </c>
       <c r="G27">
-        <v>-4.236262643618289</v>
+        <v>-4.354445681746369</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.09511374725910396</v>
       </c>
       <c r="E28">
-        <v>-29.32160409640671</v>
+        <v>-26.40158971457278</v>
       </c>
       <c r="F28">
-        <v>0.02279652367753464</v>
+        <v>0.7977532814467365</v>
       </c>
       <c r="G28">
-        <v>-4.542502332982823</v>
+        <v>-4.43178735512404</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.3815710920164094</v>
       </c>
       <c r="E29">
-        <v>-29.60032261463081</v>
+        <v>-26.63752773884641</v>
       </c>
       <c r="F29">
-        <v>0.2524191393661548</v>
+        <v>0.65936290966544</v>
       </c>
       <c r="G29">
-        <v>-4.632289679735469</v>
+        <v>-4.710569782479141</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.6237605808160295</v>
       </c>
       <c r="E30">
-        <v>-28.56584706926661</v>
+        <v>-24.61541465477934</v>
       </c>
       <c r="F30">
-        <v>-0.01050301754760268</v>
+        <v>0.7726752866943843</v>
       </c>
       <c r="G30">
-        <v>-4.554564103435342</v>
+        <v>-3.609920103800566</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8128394072534137</v>
       </c>
       <c r="E31">
-        <v>-29.4697259527236</v>
+        <v>-26.01116732800148</v>
       </c>
       <c r="F31">
-        <v>0.2584248030364512</v>
+        <v>0.7093432852807509</v>
       </c>
       <c r="G31">
-        <v>-4.149441521155381</v>
+        <v>-3.039781608074571</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.950106102756249</v>
       </c>
       <c r="E32">
-        <v>-29.29840472406542</v>
+        <v>-24.52791548000313</v>
       </c>
       <c r="F32">
-        <v>-0.2104609681745697</v>
+        <v>0.6542551962597781</v>
       </c>
       <c r="G32">
-        <v>-5.522334152621086</v>
+        <v>-4.030493958403952</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.042268222651471</v>
       </c>
       <c r="E33">
-        <v>-28.40705612818765</v>
+        <v>-25.54677231851488</v>
       </c>
       <c r="F33">
-        <v>0.004552559998278331</v>
+        <v>0.6625960276385664</v>
       </c>
       <c r="G33">
-        <v>-4.548480718664132</v>
+        <v>-4.622898823632339</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.107338840489205</v>
       </c>
       <c r="E34">
-        <v>-27.86419624957015</v>
+        <v>-24.41094499638501</v>
       </c>
       <c r="F34">
-        <v>-0.1045508822570418</v>
+        <v>0.6535767633568854</v>
       </c>
       <c r="G34">
-        <v>-4.479929437844213</v>
+        <v>-4.521889699146392</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.163258961646485</v>
       </c>
       <c r="E35">
-        <v>-28.10789154981892</v>
+        <v>-23.77017045277366</v>
       </c>
       <c r="F35">
-        <v>-0.1168554516582256</v>
+        <v>0.5367115185373339</v>
       </c>
       <c r="G35">
-        <v>-4.888083868845101</v>
+        <v>-4.050903156503698</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.232105446300436</v>
       </c>
       <c r="E36">
-        <v>-27.44603695970187</v>
+        <v>-24.50046839904265</v>
       </c>
       <c r="F36">
-        <v>-0.05858891691271118</v>
+        <v>0.6795444246998443</v>
       </c>
       <c r="G36">
-        <v>-4.571281927280713</v>
+        <v>-4.627253004641721</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.331175068710377</v>
       </c>
       <c r="E37">
-        <v>-27.24564292791444</v>
+        <v>-23.95676622425972</v>
       </c>
       <c r="F37">
-        <v>-0.001756286141442704</v>
+        <v>0.6542982713647237</v>
       </c>
       <c r="G37">
-        <v>-5.030383885435099</v>
+        <v>-4.411840809264175</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.474155885468053</v>
       </c>
       <c r="E38">
-        <v>-27.13726748796287</v>
+        <v>-24.59888119617734</v>
       </c>
       <c r="F38">
-        <v>-2.416990218893782E-05</v>
+        <v>0.8343290157499459</v>
       </c>
       <c r="G38">
-        <v>-5.175003725667625</v>
+        <v>-3.90948250729163</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.669659079359856</v>
       </c>
       <c r="E39">
-        <v>-26.76492276963019</v>
+        <v>-22.27733635377509</v>
       </c>
       <c r="F39">
-        <v>0.1156705917772068</v>
+        <v>0.5798470943033126</v>
       </c>
       <c r="G39">
-        <v>-5.774952119261175</v>
+        <v>-3.619304397460577</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.915156185950511</v>
       </c>
       <c r="E40">
-        <v>-25.72576931061607</v>
+        <v>-22.06768612111598</v>
       </c>
       <c r="F40">
-        <v>0.0657672543303562</v>
+        <v>0.8542313709696068</v>
       </c>
       <c r="G40">
-        <v>-4.792078607237308</v>
+        <v>-4.491243089781179</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.203530298261945</v>
       </c>
       <c r="E41">
-        <v>-25.90314963749652</v>
+        <v>-21.93729324053912</v>
       </c>
       <c r="F41">
-        <v>0.1178483696791667</v>
+        <v>0.5900749466256781</v>
       </c>
       <c r="G41">
-        <v>-4.960451210338654</v>
+        <v>-4.224125405069903</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.515556897185558</v>
       </c>
       <c r="E42">
-        <v>-23.97015239342639</v>
+        <v>-22.22436679330737</v>
       </c>
       <c r="F42">
-        <v>0.3655931790388317</v>
+        <v>1.141519126669309</v>
       </c>
       <c r="G42">
-        <v>-5.369977191951389</v>
+        <v>-3.620892508695349</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.830388314591633</v>
       </c>
       <c r="E43">
-        <v>-25.02474342033267</v>
+        <v>-20.96374831294813</v>
       </c>
       <c r="F43">
-        <v>-0.06726523708963321</v>
+        <v>0.5680420304460169</v>
       </c>
       <c r="G43">
-        <v>-5.098702199524298</v>
+        <v>-4.390434119810358</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.12364528993543</v>
       </c>
       <c r="E44">
-        <v>-24.55904873880587</v>
+        <v>-21.15142186124801</v>
       </c>
       <c r="F44">
-        <v>-0.1398641846383847</v>
+        <v>0.5616934226709615</v>
       </c>
       <c r="G44">
-        <v>-4.798476989278225</v>
+        <v>-3.312257527592419</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.375085658130085</v>
       </c>
       <c r="E45">
-        <v>-24.02007881936096</v>
+        <v>-19.88982523050311</v>
       </c>
       <c r="F45">
-        <v>0.1620276883726728</v>
+        <v>0.3913338677134235</v>
       </c>
       <c r="G45">
-        <v>-5.198799144416718</v>
+        <v>-3.28329746610876</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.570101769863337</v>
       </c>
       <c r="E46">
-        <v>-24.20198309177507</v>
+        <v>-20.46946537501091</v>
       </c>
       <c r="F46">
-        <v>-0.07326841565772123</v>
+        <v>0.4334497232065559</v>
       </c>
       <c r="G46">
-        <v>-4.927366653354773</v>
+        <v>-3.33766074490564</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.699553066331934</v>
       </c>
       <c r="E47">
-        <v>-23.73006628696173</v>
+        <v>-18.89861472580819</v>
       </c>
       <c r="F47">
-        <v>0.07329214381738691</v>
+        <v>0.04060559447032121</v>
       </c>
       <c r="G47">
-        <v>-4.859399429972435</v>
+        <v>-3.566010796892076</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.766310432133512</v>
       </c>
       <c r="E48">
-        <v>-23.17031520029562</v>
+        <v>-20.08942225086519</v>
       </c>
       <c r="F48">
-        <v>0.09569699696090514</v>
+        <v>0.6239162401322463</v>
       </c>
       <c r="G48">
-        <v>-5.351054387218071</v>
+        <v>-2.728098372142917</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.777409621658981</v>
       </c>
       <c r="E49">
-        <v>-22.90667650051707</v>
+        <v>-20.21867395599211</v>
       </c>
       <c r="F49">
-        <v>0.1574435031655803</v>
+        <v>0.4107499712676411</v>
       </c>
       <c r="G49">
-        <v>-4.88596091849614</v>
+        <v>-3.048322627793805</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.748002002816084</v>
       </c>
       <c r="E50">
-        <v>-22.06459317336874</v>
+        <v>-18.10137234828381</v>
       </c>
       <c r="F50">
-        <v>-0.06721470667806244</v>
+        <v>0.8292776313276745</v>
       </c>
       <c r="G50">
-        <v>-5.083142646889411</v>
+        <v>-3.78456640252357</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.693463985578196</v>
       </c>
       <c r="E51">
-        <v>-22.2813576386939</v>
+        <v>-17.43882490164359</v>
       </c>
       <c r="F51">
-        <v>-0.2636206178818252</v>
+        <v>0.5335247891387642</v>
       </c>
       <c r="G51">
-        <v>-4.746312128926172</v>
+        <v>-3.367408299563566</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.630182785405544</v>
       </c>
       <c r="E52">
-        <v>-20.50135941744693</v>
+        <v>-16.82869001316814</v>
       </c>
       <c r="F52">
-        <v>-0.1442197404423045</v>
+        <v>0.3585578546868555</v>
       </c>
       <c r="G52">
-        <v>-4.542426864886957</v>
+        <v>-2.954925937325771</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.572119574368115</v>
       </c>
       <c r="E53">
-        <v>-20.92776053000917</v>
+        <v>-17.7128292784257</v>
       </c>
       <c r="F53">
-        <v>-0.001588127558674404</v>
+        <v>0.6635453366821746</v>
       </c>
       <c r="G53">
-        <v>-5.324843989401227</v>
+        <v>-3.71412841930697</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.529607777765271</v>
       </c>
       <c r="E54">
-        <v>-20.97280978943747</v>
+        <v>-17.12080828598093</v>
       </c>
       <c r="F54">
-        <v>-0.1569616878321665</v>
+        <v>0.2283012224336472</v>
       </c>
       <c r="G54">
-        <v>-4.817022453532206</v>
+        <v>-2.562032467797861</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.512240963375102</v>
       </c>
       <c r="E55">
-        <v>-20.11230463002595</v>
+        <v>-16.38123602494424</v>
       </c>
       <c r="F55">
-        <v>-0.1391435049979491</v>
+        <v>0.1752053570164073</v>
       </c>
       <c r="G55">
-        <v>-5.020612407631073</v>
+        <v>-3.622529838253512</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.522278378090767</v>
       </c>
       <c r="E56">
-        <v>-20.52334968722818</v>
+        <v>-15.56738773323374</v>
       </c>
       <c r="F56">
-        <v>-0.06435269730139015</v>
+        <v>0.3289569739152179</v>
       </c>
       <c r="G56">
-        <v>-4.951509881589167</v>
+        <v>-3.112194886669956</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.560181198024293</v>
       </c>
       <c r="E57">
-        <v>-19.69788133121399</v>
+        <v>-17.16504242008785</v>
       </c>
       <c r="F57">
-        <v>-0.1736822838576745</v>
+        <v>0.1622861390023462</v>
       </c>
       <c r="G57">
-        <v>-5.783348765231795</v>
+        <v>-3.157308401890762</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.618589969636626</v>
       </c>
       <c r="E58">
-        <v>-19.07959066105073</v>
+        <v>-15.69815194867923</v>
       </c>
       <c r="F58">
-        <v>0.04234516601620018</v>
+        <v>0.1608580335999198</v>
       </c>
       <c r="G58">
-        <v>-5.281098743570711</v>
+        <v>-4.185413553111574</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.690026152566742</v>
       </c>
       <c r="E59">
-        <v>-18.09397282175528</v>
+        <v>-16.1478339461149</v>
       </c>
       <c r="F59">
-        <v>-0.4626507970176568</v>
+        <v>0.2840370947636091</v>
       </c>
       <c r="G59">
-        <v>-5.610142922773386</v>
+        <v>-3.607104815702562</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.762930904644812</v>
       </c>
       <c r="E60">
-        <v>-18.46010900222345</v>
+        <v>-15.20736046420192</v>
       </c>
       <c r="F60">
-        <v>-0.4479240813306872</v>
+        <v>0.1671122074910561</v>
       </c>
       <c r="G60">
-        <v>-5.729162672399124</v>
+        <v>-4.032144412848353</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.82724121160787</v>
       </c>
       <c r="E61">
-        <v>-18.22323358383023</v>
+        <v>-15.91122570768813</v>
       </c>
       <c r="F61">
-        <v>-0.03248871678530436</v>
+        <v>0.2745208100402484</v>
       </c>
       <c r="G61">
-        <v>-5.995017086810013</v>
+        <v>-4.53980516886096</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.873257879901817</v>
       </c>
       <c r="E62">
-        <v>-18.60793197925583</v>
+        <v>-15.78032563802241</v>
       </c>
       <c r="F62">
-        <v>-0.4240521895168111</v>
+        <v>0.6056192609392108</v>
       </c>
       <c r="G62">
-        <v>-5.645209337579171</v>
+        <v>-4.586700387388544</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.89113770534887</v>
       </c>
       <c r="E63">
-        <v>-18.2670827976465</v>
+        <v>-14.45183438923621</v>
       </c>
       <c r="F63">
-        <v>-0.6386026603114943</v>
+        <v>0.04220185845551586</v>
       </c>
       <c r="G63">
-        <v>-6.004086383200319</v>
+        <v>-4.05171689945044</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.874894116264846</v>
       </c>
       <c r="E64">
-        <v>-17.65981896169191</v>
+        <v>-14.9873083267472</v>
       </c>
       <c r="F64">
-        <v>-0.3013784324688295</v>
+        <v>-0.4057502401193588</v>
       </c>
       <c r="G64">
-        <v>-5.949985602128194</v>
+        <v>-5.186005661556443</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.818207204634671</v>
       </c>
       <c r="E65">
-        <v>-17.92845709677493</v>
+        <v>-15.40980589471482</v>
       </c>
       <c r="F65">
-        <v>-0.6173434392860477</v>
+        <v>0.3649255149121752</v>
       </c>
       <c r="G65">
-        <v>-6.547213863048965</v>
+        <v>-5.850961616685712</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.719957913801698</v>
       </c>
       <c r="E66">
-        <v>-17.37067136782815</v>
+        <v>-15.31768767645079</v>
       </c>
       <c r="F66">
-        <v>-0.2361908880729252</v>
+        <v>-0.4075585661596701</v>
       </c>
       <c r="G66">
-        <v>-6.757710788530462</v>
+        <v>-5.07368944757665</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.578008939802721</v>
       </c>
       <c r="E67">
-        <v>-17.29812521422527</v>
+        <v>-14.5494818742636</v>
       </c>
       <c r="F67">
-        <v>-0.5201602039570125</v>
+        <v>-0.4179338678797339</v>
       </c>
       <c r="G67">
-        <v>-6.649223760110542</v>
+        <v>-5.972678530433313</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.395277158077729</v>
       </c>
       <c r="E68">
-        <v>-17.01337476862296</v>
+        <v>-15.21376825492277</v>
       </c>
       <c r="F68">
-        <v>-0.6598370303148567</v>
+        <v>-0.1622218208399433</v>
       </c>
       <c r="G68">
-        <v>-7.18500786610915</v>
+        <v>-5.766824533458431</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.176933880409137</v>
       </c>
       <c r="E69">
-        <v>-17.71190094125413</v>
+        <v>-14.72711126721447</v>
       </c>
       <c r="F69">
-        <v>-0.7012926769879581</v>
+        <v>-0.2872108647787495</v>
       </c>
       <c r="G69">
-        <v>-6.245085544298414</v>
+        <v>-6.169971820359605</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.931342066218129</v>
       </c>
       <c r="E70">
-        <v>-17.61048123737834</v>
+        <v>-14.22989387812028</v>
       </c>
       <c r="F70">
-        <v>-0.5382973082413077</v>
+        <v>-0.8282871984089418</v>
       </c>
       <c r="G70">
-        <v>-6.7558306485769</v>
+        <v>-6.186794643294879</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.671556725630978</v>
       </c>
       <c r="E71">
-        <v>-18.14929718870699</v>
+        <v>-14.82343190935762</v>
       </c>
       <c r="F71">
-        <v>-0.7097610769467774</v>
+        <v>-0.3192148393859084</v>
       </c>
       <c r="G71">
-        <v>-7.163775081397984</v>
+        <v>-6.838163059946487</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.409508787521883</v>
       </c>
       <c r="E72">
-        <v>-18.39894290380184</v>
+        <v>-16.60501509650728</v>
       </c>
       <c r="F72">
-        <v>-0.7549559740761156</v>
+        <v>-0.6083747054159374</v>
       </c>
       <c r="G72">
-        <v>-7.128321482448183</v>
+        <v>-5.376900569441818</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.161451244566059</v>
       </c>
       <c r="E73">
-        <v>-17.78585092179938</v>
+        <v>-15.20395958022216</v>
       </c>
       <c r="F73">
-        <v>-0.6788762267008006</v>
+        <v>-0.2563177308587448</v>
       </c>
       <c r="G73">
-        <v>-7.197778380418509</v>
+        <v>-5.610205265983016</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.940115983596944</v>
       </c>
       <c r="E74">
-        <v>-17.77225644282836</v>
+        <v>-14.68582969816055</v>
       </c>
       <c r="F74">
-        <v>-0.7859418851452339</v>
+        <v>-0.4183447381115225</v>
       </c>
       <c r="G74">
-        <v>-6.571439121822345</v>
+        <v>-5.539908375293471</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.758356253696745</v>
       </c>
       <c r="E75">
-        <v>-18.06939679331565</v>
+        <v>-16.27550068533914</v>
       </c>
       <c r="F75">
-        <v>-0.4638469595472993</v>
+        <v>-0.1072811812166689</v>
       </c>
       <c r="G75">
-        <v>-6.478321335186863</v>
+        <v>-5.197352125709003</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.625126843911642</v>
       </c>
       <c r="E76">
-        <v>-17.92961638612089</v>
+        <v>-15.95619798305831</v>
       </c>
       <c r="F76">
-        <v>-0.9362069036456614</v>
+        <v>-0.805252786039296</v>
       </c>
       <c r="G76">
-        <v>-6.066619903680216</v>
+        <v>-5.552170300261117</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.544216007243084</v>
       </c>
       <c r="E77">
-        <v>-18.69716103110297</v>
+        <v>-16.96377439281694</v>
       </c>
       <c r="F77">
-        <v>-0.7792726991852951</v>
+        <v>-0.4731727197680162</v>
       </c>
       <c r="G77">
-        <v>-6.157283336589233</v>
+        <v>-6.185580591317884</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.517374464618899</v>
       </c>
       <c r="E78">
-        <v>-18.15781524831542</v>
+        <v>-16.2102951881027</v>
       </c>
       <c r="F78">
-        <v>-1.01379676479628</v>
+        <v>-0.5584050985768629</v>
       </c>
       <c r="G78">
-        <v>-6.17845377809077</v>
+        <v>-5.292878328969117</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.539915300873131</v>
       </c>
       <c r="E79">
-        <v>-19.11964048517456</v>
+        <v>-17.11560959782013</v>
       </c>
       <c r="F79">
-        <v>-1.026921417926235</v>
+        <v>-0.7399882034749313</v>
       </c>
       <c r="G79">
-        <v>-6.163734218175101</v>
+        <v>-6.226638516691215</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.605878275379113</v>
       </c>
       <c r="E80">
-        <v>-19.76140676459359</v>
+        <v>-17.33851014542568</v>
       </c>
       <c r="F80">
-        <v>-0.7983922472093105</v>
+        <v>-0.9554780429043891</v>
       </c>
       <c r="G80">
-        <v>-5.904911461566102</v>
+        <v>-5.608154502508363</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.704536365717409</v>
       </c>
       <c r="E81">
-        <v>-19.79646168188697</v>
+        <v>-18.95395267818192</v>
       </c>
       <c r="F81">
-        <v>-0.8574863209902216</v>
+        <v>-0.8091676503849264</v>
       </c>
       <c r="G81">
-        <v>-5.883097900638914</v>
+        <v>-5.79336305343122</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.822298040772525</v>
       </c>
       <c r="E82">
-        <v>-20.71121795991039</v>
+        <v>-17.63926421817109</v>
       </c>
       <c r="F82">
-        <v>-1.108299403209856</v>
+        <v>-0.8919787112753902</v>
       </c>
       <c r="G82">
-        <v>-5.212271840139798</v>
+        <v>-5.007973142184092</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.944901115636974</v>
       </c>
       <c r="E83">
-        <v>-20.85965228093381</v>
+        <v>-19.54268599849712</v>
       </c>
       <c r="F83">
-        <v>-1.124105481622673</v>
+        <v>-0.7830831892381728</v>
       </c>
       <c r="G83">
-        <v>-5.733447947755759</v>
+        <v>-4.412785801073296</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.057757826078824</v>
       </c>
       <c r="E84">
-        <v>-22.74673532704016</v>
+        <v>-20.20384320361699</v>
       </c>
       <c r="F84">
-        <v>-0.9699371959202545</v>
+        <v>-0.8362469807824423</v>
       </c>
       <c r="G84">
-        <v>-5.733237949575955</v>
+        <v>-4.260435402846718</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.151052357291563</v>
       </c>
       <c r="E85">
-        <v>-23.80563293272773</v>
+        <v>-21.42855541356942</v>
       </c>
       <c r="F85">
-        <v>-1.061592735570409</v>
+        <v>-0.4652783784193369</v>
       </c>
       <c r="G85">
-        <v>-4.786316782178923</v>
+        <v>-4.301122550183833</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.218447606335063</v>
       </c>
       <c r="E86">
-        <v>-23.68365848533113</v>
+        <v>-22.26451171538537</v>
       </c>
       <c r="F86">
-        <v>-0.6951569596354221</v>
+        <v>-0.9682572668273771</v>
       </c>
       <c r="G86">
-        <v>-4.794214682472506</v>
+        <v>-3.98937368982099</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.258421736774602</v>
       </c>
       <c r="E87">
-        <v>-25.23592427720637</v>
+        <v>-23.09472138368558</v>
       </c>
       <c r="F87">
-        <v>-0.6976702263355158</v>
+        <v>-0.646131691635539</v>
       </c>
       <c r="G87">
-        <v>-4.769110056321194</v>
+        <v>-4.839971317118962</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.275048988566961</v>
       </c>
       <c r="E88">
-        <v>-26.12170737852871</v>
+        <v>-24.52946421811376</v>
       </c>
       <c r="F88">
-        <v>-0.8679775941466773</v>
+        <v>-0.3679833134909237</v>
       </c>
       <c r="G88">
-        <v>-5.09094539175777</v>
+        <v>-4.067073016348641</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.273806015118731</v>
       </c>
       <c r="E89">
-        <v>-27.99199431454061</v>
+        <v>-26.58567218298457</v>
       </c>
       <c r="F89">
-        <v>-0.9884048187982667</v>
+        <v>-0.6212359377118026</v>
       </c>
       <c r="G89">
-        <v>-4.45329904366776</v>
+        <v>-4.547260104244018</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.264705803367382</v>
       </c>
       <c r="E90">
-        <v>-28.4849594665416</v>
+        <v>-26.21960845810053</v>
       </c>
       <c r="F90">
-        <v>-0.3659861196827741</v>
+        <v>-0.4149202672683493</v>
       </c>
       <c r="G90">
-        <v>-4.681009257450104</v>
+        <v>-3.817762521040472</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.256556270589078</v>
       </c>
       <c r="E91">
-        <v>-31.06561453471473</v>
+        <v>-28.49358620952621</v>
       </c>
       <c r="F91">
-        <v>-0.8404111837163154</v>
+        <v>-0.7928198196906782</v>
       </c>
       <c r="G91">
-        <v>-4.522372038715631</v>
+        <v>-5.216760551233119</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.259807595852789</v>
       </c>
       <c r="E92">
-        <v>-31.68997788852228</v>
+        <v>-29.19584837321371</v>
       </c>
       <c r="F92">
-        <v>-0.5607990803709535</v>
+        <v>-0.6535281841751357</v>
       </c>
       <c r="G92">
-        <v>-4.886564663263078</v>
+        <v>-4.256858871346924</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.283243908410243</v>
       </c>
       <c r="E93">
-        <v>-33.65670999971255</v>
+        <v>-30.86472237078646</v>
       </c>
       <c r="F93">
-        <v>-0.8452157146525525</v>
+        <v>-0.5659796901080616</v>
       </c>
       <c r="G93">
-        <v>-4.767731943266228</v>
+        <v>-4.693878208406247</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.332605305119424</v>
       </c>
       <c r="E94">
-        <v>-35.5734319081991</v>
+        <v>-33.92254048091081</v>
       </c>
       <c r="F94">
-        <v>-0.5992651490873513</v>
+        <v>-0.6290623529334524</v>
       </c>
       <c r="G94">
-        <v>-5.166298644870418</v>
+        <v>-4.271142028795186</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.411385169865018</v>
       </c>
       <c r="E95">
-        <v>-37.77985614861535</v>
+        <v>-37.06841476811431</v>
       </c>
       <c r="F95">
-        <v>-0.6724116474893532</v>
+        <v>-0.9248566134925026</v>
       </c>
       <c r="G95">
-        <v>-5.079398773090085</v>
+        <v>-5.666084469140359</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.518264629841398</v>
       </c>
       <c r="E96">
-        <v>-39.14380761311862</v>
+        <v>-37.76024332768814</v>
       </c>
       <c r="F96">
-        <v>-0.7411487462062534</v>
+        <v>-0.671582451719151</v>
       </c>
       <c r="G96">
-        <v>-4.650224836779394</v>
+        <v>-4.997118861265449</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.647930507137286</v>
       </c>
       <c r="E97">
-        <v>-41.98617451538004</v>
+        <v>-39.93257268730064</v>
       </c>
       <c r="F97">
-        <v>-0.6780362621543619</v>
+        <v>-0.8617250769903466</v>
       </c>
       <c r="G97">
-        <v>-5.315006887166012</v>
+        <v>-5.275835664189361</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.795550911028092</v>
       </c>
       <c r="E98">
-        <v>-44.79716814971632</v>
+        <v>-42.71860084443263</v>
       </c>
       <c r="F98">
-        <v>-0.6464257620635327</v>
+        <v>-0.5884019389670386</v>
       </c>
       <c r="G98">
-        <v>-5.585747040478915</v>
+        <v>-4.708443550908622</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.947334711376234</v>
       </c>
       <c r="E99">
-        <v>-46.09595940172322</v>
+        <v>-46.67395571016623</v>
       </c>
       <c r="F99">
-        <v>-0.7567692703208437</v>
+        <v>-1.042845952877653</v>
       </c>
       <c r="G99">
-        <v>-5.978174576545384</v>
+        <v>-6.110332337295138</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.101732150648259</v>
       </c>
       <c r="E100">
-        <v>-48.39010244790506</v>
+        <v>-46.92148889213651</v>
       </c>
       <c r="F100">
-        <v>-0.6634072938209227</v>
+        <v>-0.9401988061597523</v>
       </c>
       <c r="G100">
-        <v>-6.650677341261376</v>
+        <v>-5.189309851666804</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.237194567144032</v>
       </c>
       <c r="E101">
-        <v>-51.23044965075906</v>
+        <v>-50.61558703541959</v>
       </c>
       <c r="F101">
-        <v>-0.7454504581289912</v>
+        <v>-1.201101403345485</v>
       </c>
       <c r="G101">
-        <v>-6.57253176860164</v>
+        <v>-6.805508342986893</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.373824087383829</v>
       </c>
       <c r="E102">
-        <v>-53.74879744506065</v>
+        <v>-53.04814628600138</v>
       </c>
       <c r="F102">
-        <v>-1.051014483836659</v>
+        <v>-1.639732711904059</v>
       </c>
       <c r="G102">
-        <v>-7.664578084351352</v>
+        <v>-6.215465957281307</v>
       </c>
     </row>
   </sheetData>
